--- a/technical-triz/innovation-checklist/assets/TRU_ISQ_DE.xlsx
+++ b/technical-triz/innovation-checklist/assets/TRU_ISQ_DE.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
   <si>
     <t>Kategorie</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>Wie wird der Erfolg der Lösung gemessen?</t>
+  </si>
+  <si>
+    <t>Systemname</t>
+  </si>
+  <si>
+    <t>Datum</t>
   </si>
 </sst>
 </file>
@@ -213,8 +219,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:D22" totalsRowShown="0" dataDxfId="3">
-  <autoFilter ref="A1:D22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A4:D25" totalsRowShown="0" dataDxfId="3">
+  <autoFilter ref="A4:D25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Kategorie" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Frage" dataDxfId="1"/>
@@ -512,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.6328125" customWidth="1"/>
@@ -523,227 +529,239 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/technical-triz/innovation-checklist/assets/TRU_ISQ_DE.xlsx
+++ b/technical-triz/innovation-checklist/assets/TRU_ISQ_DE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jens\dev\github\truinorva\triz-skills\technical-triz\innovation-checklist\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075B004F-E2EF-4EFC-B991-2F0CD1CC6750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C14A38-AF8E-4E54-9448-4F49E951D200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,13 +141,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -186,6 +212,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -528,16 +560,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
